--- a/Dokumentace/User_Stories_tankovani.xlsx
+++ b/Dokumentace/User_Stories_tankovani.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jirivavra/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08615949-7BB9-8141-BC70-F455B5838397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94ECFA91-C907-0148-9661-E25D80D4EC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User Stories" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -38,9 +37,6 @@
     <t>User Story (Uživatelský příběh)</t>
   </si>
   <si>
-    <t>Akceptační kritéria (Definition of Done)</t>
-  </si>
-  <si>
     <t>Vazba (FP / NFP)</t>
   </si>
   <si>
@@ -101,7 +97,7 @@
     <t>Ruční zadání tankování</t>
   </si>
   <si>
-    <t>Jako řidič chci mít možnost zadat záznam o tankování ručně (datum, celková cena, množství paliva v litrech), abych mohl tankování заevidovat i bez fotografování stojanu.</t>
+    <t>Jako řidič chci mít možnost zadat záznam o tankování ručně (datum, celková cena, množství paliva v litrech), abych mohl tankování zaevidovat i bez fotografování stojanu.</t>
   </si>
   <si>
     <t>Formulář zvaliduje vstupy (nedovolí záporné či nulové hodnoty), uloží data s přesností na 2 desetinná místa a aktualizuje historii.</t>
@@ -116,13 +112,13 @@
     <t>Doplňující údaje a stav tachometru</t>
   </si>
   <si>
-    <t>Jako řidič chci u tankování volitelně zadat stav tachometru (ručně nebo vyfocením) a označit tankování do plna, abych měl podklady pro výpočet ujeté vzdálenosti a spotřeby.</t>
+    <t>Jako řidič chci u tankování volitelně zadat stav tachometru v kilometrech, abych měl podklady pro výpočet ujeté vzdálenosti.</t>
   </si>
   <si>
     <t>Stav tachometru se uloží v celých km. Pokud je hodnota nižší než u předchozího záznamu vozidla, aplikace zobrazí upozornění.</t>
   </si>
   <si>
-    <t>FP-05, NFP-01, NFP-08, NFP-09</t>
+    <t>FP-05, NFP-08, NFP-09</t>
   </si>
   <si>
     <t>US-06</t>
@@ -137,7 +133,7 @@
     <t>Smazání vyžaduje potvrzení uživatele. Po každé úpravě nebo smazání se do 200 ms přepočítají související statistiky a grafy.</t>
   </si>
   <si>
-    <t>FP-06, FP-07, FP-22, NFP-05</t>
+    <t>FP-06, FP-07, FP-21, NFP-05</t>
   </si>
   <si>
     <t>Fotografie stojanu a OCR</t>
@@ -254,22 +250,22 @@
     <t>Průměrná cena se počítá jako celkové výdaje / celkové množství. Grafy měsíčních součtů se vykreslí do 500 ms a okamžitě reagují na změnu dat.</t>
   </si>
   <si>
-    <t>FP-17, FP-18, FP-22, NFP-06, NFP-08</t>
+    <t>FP-17, FP-18, FP-21, NFP-06, NFP-08</t>
   </si>
   <si>
     <t>US-14</t>
   </si>
   <si>
-    <t>Výpočet ujeté vzdálenosti a spotřeby</t>
-  </si>
-  <si>
-    <t>Jako řidič chci, aby aplikace počítala ujetou vzdálenost a průměrnou spotřebu v l/100 km mezi tankováními do plna, abych znal reálnou spotřebu svého vozidla.</t>
-  </si>
-  <si>
-    <t>Spotřeba započítá i mezilehlá částečná tankování a vynechá první tankování do plna. Pokud chybí potřebné údaje nebo jsou stavy tachometru rozporné, zobrazí se srozumitelné vysvětlení místo chyby.</t>
-  </si>
-  <si>
-    <t>FP-19, FP-20, FP-21, NFP-08</t>
+    <t>Výpočet ujeté vzdálenosti</t>
+  </si>
+  <si>
+    <t>Jako řidič chci, aby aplikace počítala ujetou vzdálenost mezi dvěma po sobě následujícími záznamy s vyplněným tachometrem, abych měl přehled o ujetých kilometrech.</t>
+  </si>
+  <si>
+    <t>Vzdálenost se spočítá jako rozdíl stavů tachometru. Pokud chybí potřebné údaje nebo jsou stavy tachometru rozporné, zobrazí se srozumitelné vysvětlení místo chyby.</t>
+  </si>
+  <si>
+    <t>FP-19, FP-20, NFP-08</t>
   </si>
   <si>
     <t>Ukládání, záloha a obnova</t>
@@ -284,10 +280,10 @@
     <t>Jako řidič chci aplikaci plnohodnotně používat bez připojení k internetu a bez nutnosti přihlášení, abych mohl evidovat tankování a prohlížet statistiky kdykoliv a kdekoliv.</t>
   </si>
   <si>
-    <t>100 % základních funkcí (správa vozidel, zadávání tankování, on-device OCR, historie, statistiky a grafy) funguje v režimu Letadlo nad lokální databází Room.</t>
-  </si>
-  <si>
-    <t>FP-23, NFP-04, NFP-11</t>
+    <t>100 % základních funkcí (správa vozidel, zadávání tankování, on-device OCR, historie a statistiky) funguje v režimu Letadlo nad lokální databází Room.</t>
+  </si>
+  <si>
+    <t>FP-22, NFP-04, NFP-11</t>
   </si>
   <si>
     <t>US-16</t>
@@ -296,13 +292,16 @@
     <t>Zálohování a obnova dat přes Google Drive</t>
   </si>
   <si>
-    <t>Jako řidič chci po přihlášení ke Google účtu ručně zálohovat všechna svá vozidla a tankování na Google Drive a mít možnost je ze zálohy obnovit, abych o svá data nepřišel při ztrátě či změně telefonu.</t>
+    <t>Jako řidič chci po přihlášení ke Google účtu ručně zálohovat svá vozidla a tankování na Google Drive a mít možnost je ze zálohy obnovit, abych o data nepřišel při změně telefonu.</t>
   </si>
   <si>
     <t>Autentizace využívá OAuth 2.0 s izolovaným oprávněním pouze pro soubory aplikace. Přenos (do 5 MB) trvá max. 10 s. Před obnovou aplikace vyžádá potvrzení přepsání dat; při výpadku sítě zachová původní lokální data beze změny.</t>
   </si>
   <si>
-    <t>FP-24, FP-25, FP-26, NFP-12, NFP-13, NFP-14, NFP-15</t>
+    <t>FP-23, FP-24, FP-25, NFP-12, NFP-13, NFP-14, NFP-15</t>
+  </si>
+  <si>
+    <t>Definition of Done</t>
   </si>
 </sst>
 </file>
@@ -378,12 +377,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF7F8FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7F8FB"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -414,40 +413,40 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -679,8 +678,8 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5" ht="29" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -688,8 +687,8 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="1:5" ht="23" customHeight="1">
       <c r="A3" s="4" t="s">
@@ -697,15 +696,15 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" spans="1:5" ht="29" customHeight="1">
       <c r="A5" s="3" t="s">
@@ -717,370 +716,370 @@
       <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="27" customHeight="1">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="27" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" ht="62" customHeight="1">
+      <c r="A7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:5" ht="62" customHeight="1">
-      <c r="A7" s="9" t="s">
+      <c r="B7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="C7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="E7" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="12" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="62" customHeight="1">
+      <c r="A8" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="62" customHeight="1">
-      <c r="A8" s="13" t="s">
+      <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="C8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="D8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="E8" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="16" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="62" customHeight="1">
+      <c r="A9" s="10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="62" customHeight="1">
-      <c r="A9" s="9" t="s">
+      <c r="B9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="C9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="D9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="12" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="27" customHeight="1">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="27" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" ht="62" customHeight="1">
+      <c r="A11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-    </row>
-    <row r="11" spans="1:5" ht="62" customHeight="1">
-      <c r="A11" s="9" t="s">
+      <c r="B11" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="C11" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="12" t="s">
+    </row>
+    <row r="12" spans="1:5" ht="48" customHeight="1">
+      <c r="A12" s="7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="62" customHeight="1">
-      <c r="A12" s="13" t="s">
+      <c r="B12" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="C12" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="D12" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="E12" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="16" t="s">
+    </row>
+    <row r="13" spans="1:5" ht="62" customHeight="1">
+      <c r="A13" s="10" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="62" customHeight="1">
-      <c r="A13" s="9" t="s">
+      <c r="B13" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="C13" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="E13" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="12" t="s">
+    </row>
+    <row r="14" spans="1:5" ht="27" customHeight="1">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="27" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="8" t="s">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" ht="62" customHeight="1">
+      <c r="A15" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-    </row>
-    <row r="15" spans="1:5" ht="62" customHeight="1">
-      <c r="A15" s="9" t="s">
+      <c r="B15" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="C15" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="D15" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="E15" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="12" t="s">
+    </row>
+    <row r="16" spans="1:5" ht="62" customHeight="1">
+      <c r="A16" s="7" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="62" customHeight="1">
-      <c r="A16" s="13" t="s">
+      <c r="B16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="C16" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="D16" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="E16" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="16" t="s">
+    </row>
+    <row r="17" spans="1:5" ht="62" customHeight="1">
+      <c r="A17" s="10" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="62" customHeight="1">
-      <c r="A17" s="9" t="s">
+      <c r="B17" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="C17" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="D17" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="E17" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="12" t="s">
+    </row>
+    <row r="18" spans="1:5" ht="27" customHeight="1">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="27" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="8" t="s">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" spans="1:5" ht="62" customHeight="1">
+      <c r="A19" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19" spans="1:5" ht="62" customHeight="1">
-      <c r="A19" s="9" t="s">
+      <c r="B19" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="C19" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="D19" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="E19" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="12" t="s">
+    </row>
+    <row r="20" spans="1:5" ht="62" customHeight="1">
+      <c r="A20" s="7" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="62" customHeight="1">
-      <c r="A20" s="13" t="s">
+      <c r="B20" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="C20" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="D20" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="E20" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="16" t="s">
+    </row>
+    <row r="21" spans="1:5" ht="27" customHeight="1">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="27" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="8" t="s">
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:5" ht="62" customHeight="1">
+      <c r="A22" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5" ht="62" customHeight="1">
-      <c r="A22" s="13" t="s">
+      <c r="B22" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="C22" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="D22" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="E22" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="16" t="s">
+    </row>
+    <row r="23" spans="1:5" ht="27" customHeight="1">
+      <c r="A23" s="5"/>
+      <c r="B23" s="6" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="27" customHeight="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="8" t="s">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:5" ht="76" customHeight="1">
+      <c r="A24" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-    </row>
-    <row r="24" spans="1:5" ht="76" customHeight="1">
-      <c r="A24" s="13" t="s">
+      <c r="B24" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="C24" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="D24" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="E24" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="16" t="s">
+    </row>
+    <row r="25" spans="1:5" ht="62" customHeight="1">
+      <c r="A25" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="76" customHeight="1">
-      <c r="A25" s="9" t="s">
+      <c r="B25" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="C25" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="D25" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="E25" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="12" t="s">
+    </row>
+    <row r="26" spans="1:5" ht="27" customHeight="1">
+      <c r="A26" s="5"/>
+      <c r="B26" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="27" customHeight="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="8" t="s">
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:5" ht="62" customHeight="1">
+      <c r="A27" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-    </row>
-    <row r="27" spans="1:5" ht="62" customHeight="1">
-      <c r="A27" s="9" t="s">
+      <c r="B27" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="C27" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="D27" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="E27" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="E27" s="12" t="s">
+    </row>
+    <row r="28" spans="1:5" ht="76" customHeight="1">
+      <c r="A28" s="7" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="76" customHeight="1">
-      <c r="A28" s="13" t="s">
+      <c r="B28" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="C28" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="D28" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="E28" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E28" s="16" t="s">
-        <v>93</v>
-      </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-    </row>
-    <row r="31" spans="1:5" ht="91" customHeight="1"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+    </row>
+    <row r="31" spans="1:5" ht="59" customHeight="1"/>
     <row r="32" spans="1:5" ht="59" customHeight="1"/>
-    <row r="33" ht="59" customHeight="1"/>
-    <row r="34" ht="27" customHeight="1"/>
+    <row r="33" ht="27" customHeight="1"/>
+    <row r="34" ht="59" customHeight="1"/>
     <row r="35" ht="59" customHeight="1"/>
     <row r="36" ht="59" customHeight="1"/>
-    <row r="37" ht="59" customHeight="1"/>
-    <row r="38" ht="46" customHeight="1"/>
+    <row r="37" ht="46" customHeight="1"/>
+    <row r="38" ht="15" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
